--- a/docs/oc-regiones/pasajes-aereos-nacionales/maule.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/maule.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>202.93</v>
+        <v>201.82</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>516.83</v>
+        <v>518.67</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>183.59</v>
+        <v>184.44</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>149.7</v>
+        <v>149.08</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>194.92</v>
+        <v>194.62</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>346.04</v>
+        <v>345.5</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>259.03</v>
+        <v>260.37</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>223.05</v>
+        <v>220.17</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1411.79</v>
+        <v>1393.54</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>270.03</v>
+        <v>269.45</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>214.41</v>
+        <v>213.95</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>565.26</v>
+        <v>564.04</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>280.4</v>
+        <v>279.8</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>563.8</v>
+        <v>562.58</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>413.13</v>
+        <v>412.24</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>264.85</v>
+        <v>264.27</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>384.1</v>
+        <v>383.26</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>179.09</v>
+        <v>178.71</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>130.87</v>
+        <v>130.32</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>190.25</v>
+        <v>189.45</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1284.75</v>
+        <v>1286.54</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>279.67</v>
+        <v>278.71</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>604.3</v>
+        <v>612.4400000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>125.57</v>
+        <v>128.74</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>151.32</v>
+        <v>152.31</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>283.52</v>
+        <v>281.49</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>588.25</v>
+        <v>591.3</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>123.23</v>
+        <v>128.67</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>259.14</v>
+        <v>270.59</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>280.05</v>
+        <v>285.13</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>299.86</v>
+        <v>304.56</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>186.23</v>
+        <v>189.15</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>165.52</v>
+        <v>168.12</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>769.38</v>
+        <v>769.34</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>298.73</v>
+        <v>298.98</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>589.76</v>
+        <v>586.37</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>445.47</v>
+        <v>447.32</v>
       </c>
     </row>
     <row r="39">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>216.84</v>
+        <v>222.17</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>568.51</v>
+        <v>579.26</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>775.88</v>
+        <v>790.5599999999999</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>861.78</v>
+        <v>871.58</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>92.61</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>684.1799999999999</v>
+        <v>685.59</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>278.76</v>
+        <v>280.88</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>156.47</v>
+        <v>157.64</v>
       </c>
     </row>
     <row r="47">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>500.27</v>
+        <v>495.28</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>532.99</v>
+        <v>527.67</v>
       </c>
     </row>
     <row r="49">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>266.49</v>
+        <v>265.32</v>
       </c>
     </row>
     <row r="50">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>250.13</v>
+        <v>249.04</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>408.73</v>
+        <v>406.94</v>
       </c>
     </row>
     <row r="52">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>686.05</v>
+        <v>683.04</v>
       </c>
     </row>
     <row r="53">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1004.73</v>
+        <v>993.8099999999999</v>
       </c>
     </row>
     <row r="54">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>440.52</v>
+        <v>439.52</v>
       </c>
     </row>
     <row r="55">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>162.28</v>
+        <v>164.6</v>
       </c>
     </row>
     <row r="56">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1580.79</v>
+        <v>1599.33</v>
       </c>
     </row>
     <row r="57">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>357.65</v>
+        <v>363.69</v>
       </c>
     </row>
     <row r="58">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>424.76</v>
+        <v>429.08</v>
       </c>
     </row>
     <row r="59">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>486.53</v>
+        <v>491.1</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>509.67</v>
+        <v>514.45</v>
       </c>
     </row>
     <row r="61">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>802</v>
+        <v>788.45</v>
       </c>
     </row>
     <row r="62">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>309.67</v>
+        <v>305.28</v>
       </c>
     </row>
     <row r="63">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>77.42</v>
+        <v>76.31999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>409.77</v>
+        <v>404.14</v>
       </c>
     </row>
     <row r="65">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>279.04</v>
+        <v>277.31</v>
       </c>
     </row>
     <row r="66">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1252.77</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="67">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>71.62</v>
+        <v>71.18000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>436.38</v>
+        <v>438.36</v>
       </c>
     </row>
     <row r="69">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1309.13</v>
+        <v>1315.07</v>
       </c>
     </row>
     <row r="70">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>475.68</v>
+        <v>478.97</v>
       </c>
     </row>
     <row r="71">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>689.73</v>
+        <v>694.35</v>
       </c>
     </row>
     <row r="72">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>254.21</v>
+        <v>255.91</v>
       </c>
     </row>
     <row r="73">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>212.4</v>
+        <v>213.82</v>
       </c>
     </row>
     <row r="74">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>714.73</v>
+        <v>712.47</v>
       </c>
     </row>
     <row r="75">
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>7.52</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="76">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>177.71</v>
+        <v>175.64</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/pasajes-aereos-nacionales/maule.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1087105-31-CM25</t>
+          <t>1068241-2-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>201.82</v>
+        <v>370.58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1607-211-CM25</t>
+          <t>1087105-5-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>518.67</v>
+        <v>223.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1087105-34-CM25</t>
+          <t>1068241-5-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>184.44</v>
+        <v>92.45999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1087105-35-CM25</t>
+          <t>1087105-7-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>149.08</v>
+        <v>320.56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1596-374-CM25</t>
+          <t>1068241-10-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>194.62</v>
+        <v>160.48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1596-375-CM25</t>
+          <t>1087105-14-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>345.5</v>
+        <v>437.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1607-224-CM25</t>
+          <t>1391-1688-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>260.37</v>
+        <v>497.98</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1607-229-CM25</t>
+          <t>1087105-31-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>220.17</v>
+        <v>201.82</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1607-230-CM25</t>
+          <t>1607-211-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1393.54</v>
+        <v>518.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1607-243-CM25</t>
+          <t>1087105-34-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>269.45</v>
+        <v>184.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1607-242-CM25</t>
+          <t>1087105-35-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>213.95</v>
+        <v>149.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1607-241-CM25</t>
+          <t>1596-374-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>564.04</v>
+        <v>194.62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1607-240-CM25</t>
+          <t>1596-375-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>279.8</v>
+        <v>345.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1607-236-CM25</t>
+          <t>1607-224-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>562.58</v>
+        <v>260.37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1607-238-CM25</t>
+          <t>1607-229-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>412.24</v>
+        <v>220.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1607-237-CM25</t>
+          <t>1607-230-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>264.27</v>
+        <v>1393.54</v>
       </c>
     </row>
     <row r="18">
@@ -1551,7 +1551,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1607-239-CM25</t>
+          <t>1607-240-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>178.71</v>
+        <v>279.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1607-248-CM25</t>
+          <t>1607-242-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>130.32</v>
+        <v>213.95</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1607-247-CM25</t>
+          <t>1607-241-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>189.45</v>
+        <v>564.04</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4134-28-CM26</t>
+          <t>1607-239-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1286.54</v>
+        <v>178.71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1087105-1-CM26</t>
+          <t>1607-237-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>278.71</v>
+        <v>264.27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1607-2-CM26</t>
+          <t>1607-236-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,17 +1866,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1911,33 +1911,33 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>612.4400000000001</v>
+        <v>562.58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1607-6-SE26</t>
+          <t>1607-243-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1965,24 +1965,20 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>128.74</v>
+        <v>269.45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1234683-13-CM26</t>
+          <t>1607-238-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1992,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2007,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65.145.951-6</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL  DE DEPORTES  DE SAN CLEMENTE</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2022,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>152.31</v>
+        <v>412.24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1087105-7-CM26</t>
+          <t>1607-247-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2053,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2068,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>281.49</v>
+        <v>189.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1607-19-CM26</t>
+          <t>1607-248-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2114,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2159,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>591.3</v>
+        <v>130.32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1978-158-CM26</t>
+          <t>4134-28-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2175,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>I. Municipalidad Sagrada Familia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2220,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>128.67</v>
+        <v>1286.54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1978-157-CM26</t>
+          <t>1087105-1-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2266,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>270.59</v>
+        <v>278.71</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2177-18-CM26</t>
+          <t>1607-2-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2297,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2312,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2342,33 +2338,33 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>285.13</v>
+        <v>612.4400000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1607-24-CM26</t>
+          <t>1607-6-SE26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-23-LP10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2396,20 +2392,24 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>304.56</v>
+        <v>128.74</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1607-25-CM26</t>
+          <t>1234683-13-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2419,27 +2419,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>65.145.951-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>CORPORACION MUNICIPAL  DE DEPORTES  DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>JETSMART</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>189.15</v>
+        <v>152.31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1607-26-CM26</t>
+          <t>1087105-7-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>168.12</v>
+        <v>281.49</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1596-78-CM26</t>
+          <t>1607-19-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2541,27 +2541,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>769.34</v>
+        <v>591.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1607-30-CM26</t>
+          <t>1978-157-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>298.98</v>
+        <v>270.59</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1607-32-CM26</t>
+          <t>1978-158-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>586.37</v>
+        <v>128.67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3385-71-CM26</t>
+          <t>2177-18-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2724,27 +2724,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>447.32</v>
+        <v>285.13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1607-34-CM26</t>
+          <t>1607-25-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>222.17</v>
+        <v>189.15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1607-39-CM26</t>
+          <t>1607-24-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>579.26</v>
+        <v>304.56</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1607-40-CM26</t>
+          <t>1607-26-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2952,13 +2952,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>790.5599999999999</v>
+        <v>168.12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1607-41-CM26</t>
+          <t>1596-78-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2968,27 +2968,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>871.58</v>
+        <v>769.34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2177-44-CM26</t>
+          <t>1607-30-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3029,27 +3029,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>93</v>
+        <v>298.98</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1607-45-CM26</t>
+          <t>1607-32-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>685.59</v>
+        <v>586.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1607-48-CM26</t>
+          <t>3385-71-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3151,27 +3151,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>280.88</v>
+        <v>447.32</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1978-424-CM26</t>
+          <t>1607-34-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3257,13 +3257,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>157.64</v>
+        <v>222.17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1596-128-CM26</t>
+          <t>1607-39-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3273,27 +3273,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>495.28</v>
+        <v>579.26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1596-127-CM26</t>
+          <t>1607-40-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3334,27 +3334,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3379,13 +3379,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>527.67</v>
+        <v>790.5599999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1596-131-CM26</t>
+          <t>1607-41-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3395,27 +3395,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>265.32</v>
+        <v>871.58</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1596-132-CM26</t>
+          <t>2177-44-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3456,12 +3456,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>249.04</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4885-60-CM26</t>
+          <t>1607-45-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.976.200-2</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Maule</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>406.94</v>
+        <v>685.59</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4885-61-CM26</t>
+          <t>1607-48-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3583,22 +3583,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.976.200-2</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Maule</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3623,13 +3623,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>683.04</v>
+        <v>280.88</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1596-134-CM26</t>
+          <t>1978-424-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3644,22 +3644,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>993.8099999999999</v>
+        <v>157.64</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4134-334-CM26</t>
+          <t>1596-127-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3705,22 +3705,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3745,13 +3745,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>439.52</v>
+        <v>527.67</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1607-64-CM26</t>
+          <t>1596-128-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>164.6</v>
+        <v>495.28</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3469-244-CM26</t>
+          <t>1596-131-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3822,27 +3822,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1599.33</v>
+        <v>265.32</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1347775-9-CM26</t>
+          <t>1596-132-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>363.69</v>
+        <v>249.04</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2595-226-CM26</t>
+          <t>4885-60-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>Subsecretaria de las Culturas y las Artes Región del Maule</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3989,13 +3989,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>429.08</v>
+        <v>406.94</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1596-147-CM26</t>
+          <t>4885-61-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4005,12 +4005,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>Subsecretaria de las Culturas y las Artes Región del Maule</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4050,13 +4050,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>491.1</v>
+        <v>683.04</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1596-148-CM26</t>
+          <t>1596-134-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4111,13 +4111,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>514.45</v>
+        <v>993.8099999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3206-211-CM26</t>
+          <t>4134-334-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.264.500-6</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+          <t>I. Municipalidad Sagrada Familia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>788.45</v>
+        <v>439.52</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4134-394-CM26</t>
+          <t>1607-64-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4193,22 +4193,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4233,13 +4233,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>305.28</v>
+        <v>164.6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4134-395-CM26</t>
+          <t>3469-244-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>69.120.300-k</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4294,13 +4294,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>76.31999999999999</v>
+        <v>1599.33</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2291-1051-CM26</t>
+          <t>1347775-9-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>404.14</v>
+        <v>363.69</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1607-72-CM26</t>
+          <t>2595-226-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>277.31</v>
+        <v>429.08</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1133353-38-CM26</t>
+          <t>1596-147-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4437,22 +4437,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1245</v>
+        <v>491.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1978-571-CM26</t>
+          <t>1596-148-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>71.18000000000001</v>
+        <v>514.45</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3843-144-CM26</t>
+          <t>3206-211-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4559,22 +4559,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>438.36</v>
+        <v>788.45</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3876-118-CM26</t>
+          <t>4134-394-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I. Municipalidad Sagrada Familia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JETSMART</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1315.07</v>
+        <v>305.28</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2177-61-CM26</t>
+          <t>4134-395-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4681,22 +4681,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I. Municipalidad Sagrada Familia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JETSMART</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4721,13 +4721,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>478.97</v>
+        <v>76.31999999999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1230851-52-CM26</t>
+          <t>2291-1051-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4737,27 +4737,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>65.061.839-4</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4782,13 +4782,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>694.35</v>
+        <v>404.14</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1230851-55-CM26</t>
+          <t>1133353-38-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>65.061.839-4</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4843,13 +4843,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>255.91</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1230851-56-CM26</t>
+          <t>1607-72-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4859,27 +4859,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>65.061.839-4</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4904,13 +4904,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>213.82</v>
+        <v>277.31</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4134-515-CM26</t>
+          <t>1978-571-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4965,28 +4965,28 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>712.47</v>
+        <v>71.18000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4134-523-SE26</t>
+          <t>3843-144-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5011,32 +5011,28 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>7.4</v>
+        <v>438.36</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1607-91-CM26</t>
+          <t>3876-118-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5046,12 +5042,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5061,12 +5057,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5091,6 +5087,437 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
+        <v>1315.07</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2177-61-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>478.97</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1230851-52-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>65.061.839-4</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>694.35</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1230851-55-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>65.061.839-4</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>255.91</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1230851-56-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>65.061.839-4</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>213.82</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>4134-515-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>69.110.200-9</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>I. Municipalidad Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>JETSMART</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>712.47</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>4134-523-SE26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-23-LP10</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>69.110.200-9</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>I. Municipalidad Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>JETSMART</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1607-91-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Superintendencia de Seguridad Social</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
         <v>175.64</v>
       </c>
     </row>

--- a/docs/oc-regiones/pasajes-aereos-nacionales/maule.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/maule.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maule" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Maule" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -697,7 +697,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1087105-7-CM25</t>
+          <t>1391-376-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>320.56</v>
+        <v>126.28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1068241-10-CM25</t>
+          <t>1978-245-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>160.48</v>
+        <v>338.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1087105-14-CM25</t>
+          <t>1087105-7-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>437.49</v>
+        <v>320.56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1391-1688-CM25</t>
+          <t>732-169-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>497.98</v>
+        <v>55.63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1087105-31-CM25</t>
+          <t>732-187-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>201.82</v>
+        <v>206.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1607-211-CM25</t>
+          <t>732-184-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>518.67</v>
+        <v>154.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1087105-34-CM25</t>
+          <t>1068241-10-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>184.44</v>
+        <v>160.48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1087105-35-CM25</t>
+          <t>732-196-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>149.08</v>
+        <v>99.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1596-374-CM25</t>
+          <t>732-197-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>194.62</v>
+        <v>203.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1596-375-CM25</t>
+          <t>732-201-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>345.5</v>
+        <v>337.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1607-224-CM25</t>
+          <t>732-207-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>260.37</v>
+        <v>199.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1607-229-CM25</t>
+          <t>1596-94-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>220.17</v>
+        <v>439.87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1607-230-CM25</t>
+          <t>732-213-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1393.54</v>
+        <v>290.14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1607-244-CM25</t>
+          <t>732-215-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>383.26</v>
+        <v>283.01</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1607-240-CM25</t>
+          <t>2318-365-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>279.8</v>
+        <v>2329.94</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1607-242-CM25</t>
+          <t>2318-366-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>213.95</v>
+        <v>514.22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1607-241-CM25</t>
+          <t>732-226-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>564.04</v>
+        <v>307.98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1607-239-CM25</t>
+          <t>732-224-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>178.71</v>
+        <v>615.96</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1607-237-CM25</t>
+          <t>732-230-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>264.27</v>
+        <v>186.76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1607-236-CM25</t>
+          <t>732-231-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>562.58</v>
+        <v>841.79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1607-243-CM25</t>
+          <t>732-240-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>269.45</v>
+        <v>216.33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1607-238-CM25</t>
+          <t>2177-51-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>412.24</v>
+        <v>316.35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1607-247-CM25</t>
+          <t>1087105-14-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>189.45</v>
+        <v>437.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1607-248-CM25</t>
+          <t>1208102-21-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>130.32</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4134-28-CM26</t>
+          <t>1208102-24-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1286.54</v>
+        <v>183.78</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1087105-1-CM26</t>
+          <t>1872-6-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>60.704.000-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>278.71</v>
+        <v>102.57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1607-2-CM26</t>
+          <t>1596-164-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,28 +2338,28 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>612.4400000000001</v>
+        <v>104.16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1607-6-SE26</t>
+          <t>2177-66-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2392,24 +2392,20 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>128.74</v>
+        <v>256.96</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1234683-13-CM26</t>
+          <t>1230851-29-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2419,27 +2415,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>65.145.951-6</t>
+          <t>65.061.839-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL  DE DEPORTES  DE SAN CLEMENTE</t>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2449,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>152.31</v>
+        <v>464.31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1087105-7-CM26</t>
+          <t>1230851-30-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2480,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2495,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>65.061.839-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2525,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>281.49</v>
+        <v>227.66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1607-19-CM26</t>
+          <t>1230851-32-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2541,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2556,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>65.061.839-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2586,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>591.3</v>
+        <v>143.72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1978-157-CM26</t>
+          <t>3206-228-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2602,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2617,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2632,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2647,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>270.59</v>
+        <v>1397.95</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1978-158-CM26</t>
+          <t>1596-189-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2663,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2678,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2708,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>128.67</v>
+        <v>252.53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2177-18-CM26</t>
+          <t>2318-712-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2724,27 +2720,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2754,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2769,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>285.13</v>
+        <v>594.88</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1607-25-CM26</t>
+          <t>4885-69-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2785,27 +2781,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2815,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2830,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>189.15</v>
+        <v>179.95</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1607-24-CM26</t>
+          <t>4885-70-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2846,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2861,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2891,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>304.56</v>
+        <v>1704.37</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1607-26-CM26</t>
+          <t>1391-1611-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2907,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2922,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2937,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2952,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>168.12</v>
+        <v>253.91</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1596-78-CM26</t>
+          <t>1596-231-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2968,17 +2964,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3013,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>769.34</v>
+        <v>779.88</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1607-30-CM26</t>
+          <t>1391-1688-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3029,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3044,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3074,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>298.98</v>
+        <v>497.98</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1607-32-CM26</t>
+          <t>2177-82-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3090,27 +3086,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3135,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>586.37</v>
+        <v>316.89</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3385-71-CM26</t>
+          <t>1208102-54-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3151,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3166,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3196,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>447.32</v>
+        <v>160.36</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1607-34-CM26</t>
+          <t>4885-139-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3212,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3227,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3257,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>222.17</v>
+        <v>711.89</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1607-39-CM26</t>
+          <t>4885-140-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3273,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3288,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3303,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3318,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>579.26</v>
+        <v>235.91</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1607-40-CM26</t>
+          <t>1872-14-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3334,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3349,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>60.704.000-1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3364,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3379,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>790.5599999999999</v>
+        <v>437.36</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1607-41-CM26</t>
+          <t>4885-192-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3395,12 +3391,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3410,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3440,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>871.58</v>
+        <v>1792.81</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2177-44-CM26</t>
+          <t>4885-195-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3456,27 +3452,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3501,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>93</v>
+        <v>452.96</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1607-45-CM26</t>
+          <t>1087105-31-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3517,12 +3513,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3532,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3547,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3562,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>685.59</v>
+        <v>201.82</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1607-48-CM26</t>
+          <t>1607-211-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3578,17 +3574,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3608,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3623,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>280.88</v>
+        <v>518.67</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1978-424-CM26</t>
+          <t>1087105-34-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3639,12 +3635,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3654,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3684,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>157.64</v>
+        <v>184.44</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1596-127-CM26</t>
+          <t>1087105-35-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3700,27 +3696,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3730,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3745,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>527.67</v>
+        <v>149.08</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1596-128-CM26</t>
+          <t>1596-375-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3761,17 +3757,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3806,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>495.28</v>
+        <v>345.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1596-131-CM26</t>
+          <t>1596-374-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3822,17 +3818,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3867,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>265.32</v>
+        <v>194.62</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1596-132-CM26</t>
+          <t>1607-224-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3883,27 +3879,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3913,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3928,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>249.04</v>
+        <v>260.37</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4885-60-CM26</t>
+          <t>1607-229-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3944,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3959,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.976.200-2</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Maule</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3989,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>406.94</v>
+        <v>220.17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4885-61-CM26</t>
+          <t>1607-230-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4005,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4020,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.976.200-2</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Maule</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4050,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>683.04</v>
+        <v>1393.54</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1596-134-CM26</t>
+          <t>1607-239-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4066,27 +4062,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4111,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>993.8099999999999</v>
+        <v>178.71</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4134-334-CM26</t>
+          <t>1607-238-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4127,27 +4123,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4172,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>439.52</v>
+        <v>412.24</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1607-64-CM26</t>
+          <t>1607-236-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4188,17 +4184,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4233,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>164.6</v>
+        <v>562.58</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3469-244-CM26</t>
+          <t>1607-240-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4249,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4264,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4294,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1599.33</v>
+        <v>279.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1347775-9-CM26</t>
+          <t>1607-241-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4310,12 +4306,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4325,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4355,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>363.69</v>
+        <v>564.04</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2595-226-CM26</t>
+          <t>1607-242-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4371,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4386,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4416,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>429.08</v>
+        <v>213.95</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1596-147-CM26</t>
+          <t>1607-243-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4432,12 +4428,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4447,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4477,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>491.1</v>
+        <v>269.45</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1596-148-CM26</t>
+          <t>1607-244-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4493,27 +4489,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4523,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4538,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>514.45</v>
+        <v>383.26</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3206-211-CM26</t>
+          <t>1607-237-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4554,12 +4550,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4569,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.264.500-6</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4599,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>788.45</v>
+        <v>264.27</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4134-394-CM26</t>
+          <t>1607-247-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4615,12 +4611,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4630,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4645,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4660,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>305.28</v>
+        <v>189.45</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4134-395-CM26</t>
+          <t>1607-248-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4676,12 +4672,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4691,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4706,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4721,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>76.31999999999999</v>
+        <v>130.32</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2291-1051-CM26</t>
+          <t>4134-28-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4737,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4752,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I. Municipalidad Sagrada Familia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4782,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>404.14</v>
+        <v>1286.54</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1133353-38-CM26</t>
+          <t>1087105-1-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4798,27 +4794,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4828,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4843,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1245</v>
+        <v>278.71</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1607-72-CM26</t>
+          <t>1607-2-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4859,17 +4855,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4904,28 +4900,28 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>277.31</v>
+        <v>612.4400000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1978-571-CM26</t>
+          <t>1607-6-SE26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-23-LP10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4935,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4950,28 +4946,32 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>71.18000000000001</v>
+        <v>128.74</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3843-144-CM26</t>
+          <t>1234683-13-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>65.145.951-6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>CORPORACION MUNICIPAL  DE DEPORTES  DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JETSMART</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5026,13 +5026,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>438.36</v>
+        <v>152.31</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3876-118-CM26</t>
+          <t>1087105-7-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1315.07</v>
+        <v>281.49</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2177-61-CM26</t>
+          <t>1607-19-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5103,27 +5103,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>478.97</v>
+        <v>591.3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1230851-52-CM26</t>
+          <t>1978-157-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5164,27 +5164,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>65.061.839-4</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5209,13 +5209,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>694.35</v>
+        <v>270.59</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1230851-55-CM26</t>
+          <t>1978-158-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5225,27 +5225,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>65.061.839-4</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5270,13 +5270,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>255.91</v>
+        <v>128.67</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1230851-56-CM26</t>
+          <t>2177-18-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>65.061.839-4</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>213.82</v>
+        <v>285.13</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4134-515-CM26</t>
+          <t>1607-26-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5347,27 +5347,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5392,43 +5392,43 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>712.47</v>
+        <v>168.12</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4134-523-SE26</t>
+          <t>1607-24-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5438,32 +5438,28 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>7.4</v>
+        <v>304.56</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1607-91-CM26</t>
+          <t>1607-25-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5473,12 +5469,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5503,12 +5499,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5518,7 +5514,2817 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
+        <v>189.15</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1596-78-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>769.34</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1607-30-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Superintendencia de Seguridad Social</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>298.98</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1607-32-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Superintendencia de Seguridad Social</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>586.37</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>3385-71-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>61.101.023-0</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>447.32</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1607-34-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Superintendencia de Seguridad Social</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>222.17</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1607-39-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Superintendencia de Seguridad Social</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>579.26</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1607-40-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Superintendencia de Seguridad Social</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>790.5599999999999</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1607-41-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Superintendencia de Seguridad Social</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>871.58</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2177-44-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1607-45-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Superintendencia de Seguridad Social</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>685.59</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1607-48-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Superintendencia de Seguridad Social</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>280.88</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1978-424-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>61.606.900-4</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>157.64</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1596-128-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>495.28</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1596-127-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>527.67</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1596-131-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>265.32</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1596-132-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>249.04</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>4885-60-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>61.976.200-2</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Subsecretaria de las Culturas y las Artes Región del Maule</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>406.94</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>4885-61-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>61.976.200-2</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Subsecretaria de las Culturas y las Artes Región del Maule</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>683.04</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1596-134-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>993.8099999999999</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>4134-334-CM26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>69.110.200-9</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>I. Municipalidad Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>439.52</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1607-64-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Superintendencia de Seguridad Social</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>164.6</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>3469-244-CM26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>69.120.300-k</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>1599.33</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1347775-9-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>363.69</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2595-226-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>69.130.700-K</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>429.08</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1596-147-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>491.1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1596-148-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>514.45</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>3206-211-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>69.264.500-6</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>788.45</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>4134-394-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>69.110.200-9</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>I. Municipalidad Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>JETSMART</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>305.28</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>4134-395-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>69.110.200-9</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>I. Municipalidad Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>JETSMART</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>76.31999999999999</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2291-1051-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>404.14</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1978-571-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>61.606.900-4</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>71.18000000000001</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1607-72-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Superintendencia de Seguridad Social</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>277.31</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1133353-38-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>69.100.400-7</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>3876-118-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>69.100.400-7</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>1315.07</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>3843-144-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>69.100.400-7</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>438.36</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2177-61-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>478.97</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1230851-52-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>65.061.839-4</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>694.35</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1230851-55-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>65.061.839-4</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>255.91</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1230851-56-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>65.061.839-4</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>213.82</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>4134-515-CM26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>69.110.200-9</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>I. Municipalidad Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>JETSMART</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>712.47</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>4134-523-SE26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2239-23-LP10</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>69.110.200-9</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>I. Municipalidad Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>JETSMART</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1607-91-CM26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Superintendencia de Seguridad Social</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="n">
         <v>175.64</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>4885-100-CM26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>61.976.200-2</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>716.61</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>4885-101-CM26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>61.976.200-2</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>653.02</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1596-221-CM26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>214.75</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1596-223-CM26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>65.44</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/pasajes-aereos-nacionales/maule.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1068241-2-CM25</t>
+          <t>1087105-5-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ene-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>370.58</v>
+        <v>223.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1087105-5-CM25</t>
+          <t>1068241-5-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,22 +590,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>223.67</v>
+        <v>92.45999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1068241-5-CM25</t>
+          <t>1391-376-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>92.45999999999999</v>
+        <v>126.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1391-376-CM25</t>
+          <t>1087105-7-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>126.28</v>
+        <v>320.56</v>
       </c>
     </row>
     <row r="6">
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1087105-7-CM25</t>
+          <t>732-169-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>320.56</v>
+        <v>55.63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>732-169-CM25</t>
+          <t>732-184-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>55.63</v>
+        <v>154.67</v>
       </c>
     </row>
     <row r="9">
@@ -1002,7 +1002,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>732-184-CM25</t>
+          <t>1068241-10-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.701.000-3</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>154.67</v>
+        <v>160.48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1068241-10-CM25</t>
+          <t>732-197-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>160.48</v>
+        <v>203.6</v>
       </c>
     </row>
     <row r="12">
@@ -1185,7 +1185,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>732-197-CM25</t>
+          <t>732-201-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>203.6</v>
+        <v>337.35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>732-201-CM25</t>
+          <t>732-207-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>337.35</v>
+        <v>199.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>732-207-CM25</t>
+          <t>732-215-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>199.42</v>
+        <v>283.01</v>
       </c>
     </row>
     <row r="16">
@@ -1490,7 +1490,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>732-215-CM25</t>
+          <t>732-224-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>283.01</v>
+        <v>615.96</v>
       </c>
     </row>
     <row r="19">
@@ -1734,7 +1734,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>732-224-CM25</t>
+          <t>732-231-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>615.96</v>
+        <v>841.79</v>
       </c>
     </row>
     <row r="23">
@@ -1856,7 +1856,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>732-231-CM25</t>
+          <t>732-240-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>841.79</v>
+        <v>216.33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>732-240-CM25</t>
+          <t>2177-51-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.701.000-3</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>216.33</v>
+        <v>316.35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2177-51-CM25</t>
+          <t>1208102-21-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,22 +1993,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>316.35</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="27">
@@ -2100,7 +2100,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1208102-21-CM25</t>
+          <t>1208102-24-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>309.99</v>
+        <v>183.78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1208102-24-CM25</t>
+          <t>1872-6-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.704.000-1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>183.78</v>
+        <v>102.57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1872-6-CM25</t>
+          <t>1596-164-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.704.000-1</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE TURISMO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>102.57</v>
+        <v>104.16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1596-164-CM25</t>
+          <t>2177-66-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,22 +2298,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>104.16</v>
+        <v>256.96</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2177-66-CM25</t>
+          <t>1230851-30-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,27 +2354,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>65.061.839-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>256.96</v>
+        <v>227.66</v>
       </c>
     </row>
     <row r="33">
@@ -2466,7 +2466,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1230851-30-CM25</t>
+          <t>1230851-32-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>227.66</v>
+        <v>143.72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1230851-32-CM25</t>
+          <t>3206-228-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>65.061.839-4</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>143.72</v>
+        <v>1397.95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3206-228-CM25</t>
+          <t>1596-189-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.264.500-6</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1397.95</v>
+        <v>252.53</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1596-189-CM25</t>
+          <t>2318-712-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>252.53</v>
+        <v>594.88</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2318-712-CM25</t>
+          <t>4885-69-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,22 +2725,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>594.88</v>
+        <v>179.95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4885-69-CM25</t>
+          <t>4885-70-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>179.95</v>
+        <v>1704.37</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4885-70-CM25</t>
+          <t>1391-1611-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.976.200-2</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1704.37</v>
+        <v>253.91</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1391-1611-CM25</t>
+          <t>1596-231-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>253.91</v>
+        <v>779.88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1596-231-CM25</t>
+          <t>1391-1688-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>779.88</v>
+        <v>497.98</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1391-1688-CM25</t>
+          <t>2177-82-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>497.98</v>
+        <v>316.89</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2177-82-CM25</t>
+          <t>1208102-54-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,27 +3086,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>316.89</v>
+        <v>160.36</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1208102-54-CM25</t>
+          <t>4885-139-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>160.36</v>
+        <v>711.89</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4885-139-CM25</t>
+          <t>4885-140-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>711.89</v>
+        <v>235.91</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4885-140-CM25</t>
+          <t>1872-14-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.976.200-2</t>
+          <t>60.704.000-1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>235.91</v>
+        <v>437.36</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1872-14-CM25</t>
+          <t>4885-192-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.704.000-1</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE TURISMO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>437.36</v>
+        <v>1792.81</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4885-192-CM25</t>
+          <t>4885-195-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1792.81</v>
+        <v>452.96</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4885-195-CM25</t>
+          <t>1596-375-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.976.200-2</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>452.96</v>
+        <v>345.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1087105-31-CM25</t>
+          <t>1596-374-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>201.82</v>
+        <v>194.62</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1607-211-CM25</t>
+          <t>4134-28-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>518.67</v>
+        <v>1286.54</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1087105-34-CM25</t>
+          <t>1234683-13-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,27 +3635,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>65.145.951-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>CORPORACION MUNICIPAL  DE DEPORTES  DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>184.44</v>
+        <v>152.31</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1087105-35-CM25</t>
+          <t>1978-157-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>149.08</v>
+        <v>270.59</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1596-375-CM25</t>
+          <t>1978-158-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>345.5</v>
+        <v>128.67</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1596-374-CM25</t>
+          <t>2177-18-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>194.62</v>
+        <v>285.13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1607-224-CM25</t>
+          <t>1596-78-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,27 +3879,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>260.37</v>
+        <v>769.34</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1607-229-CM25</t>
+          <t>3385-71-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>220.17</v>
+        <v>447.32</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1607-230-CM25</t>
+          <t>2177-44-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,27 +4001,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1393.54</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1607-239-CM25</t>
+          <t>1978-424-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>178.71</v>
+        <v>157.64</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1607-238-CM25</t>
+          <t>1596-127-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>412.24</v>
+        <v>527.67</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1607-236-CM25</t>
+          <t>1596-128-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,27 +4184,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>562.58</v>
+        <v>495.28</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1607-240-CM25</t>
+          <t>1596-131-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,27 +4245,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>279.8</v>
+        <v>265.32</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1607-241-CM25</t>
+          <t>1596-132-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>564.04</v>
+        <v>249.04</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1607-242-CM25</t>
+          <t>4885-60-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>213.95</v>
+        <v>406.94</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1607-243-CM25</t>
+          <t>4885-61-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>269.45</v>
+        <v>683.04</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1607-244-CM25</t>
+          <t>1596-134-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,27 +4489,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>383.26</v>
+        <v>993.8099999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1607-237-CM25</t>
+          <t>4134-334-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>264.27</v>
+        <v>439.52</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1607-247-CM25</t>
+          <t>3469-244-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>69.120.300-k</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>189.45</v>
+        <v>1599.33</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1607-248-CM25</t>
+          <t>2595-226-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>130.32</v>
+        <v>429.08</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4134-28-CM26</t>
+          <t>1596-147-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1286.54</v>
+        <v>491.1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1087105-1-CM26</t>
+          <t>1596-148-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,27 +4794,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>278.71</v>
+        <v>514.45</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1607-2-CM26</t>
+          <t>3206-211-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,27 +4855,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,43 +4900,43 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>612.4400000000001</v>
+        <v>788.45</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1607-6-SE26</t>
+          <t>4134-394-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,32 +4946,28 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>128.74</v>
+        <v>305.28</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1234683-13-CM26</t>
+          <t>4134-395-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4981,27 +4977,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>65.145.951-6</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL  DE DEPORTES  DE SAN CLEMENTE</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5011,7 +5007,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5026,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>152.31</v>
+        <v>76.31999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1087105-7-CM26</t>
+          <t>2291-1051-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5042,12 +5038,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5057,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5087,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>281.49</v>
+        <v>404.14</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1607-19-CM26</t>
+          <t>1133353-38-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5103,12 +5099,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5118,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5148,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>591.3</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1978-157-CM26</t>
+          <t>1978-571-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5164,17 +5160,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5194,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5209,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>270.59</v>
+        <v>71.18000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1978-158-CM26</t>
+          <t>3843-144-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5225,27 +5221,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5270,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>128.67</v>
+        <v>438.36</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2177-18-CM26</t>
+          <t>3876-118-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5286,27 +5282,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5331,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>285.13</v>
+        <v>1315.07</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1607-26-CM26</t>
+          <t>2177-61-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5347,27 +5343,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5377,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5392,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>168.12</v>
+        <v>478.97</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1607-24-CM26</t>
+          <t>1230851-52-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5408,27 +5404,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>65.061.839-4</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5453,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>304.56</v>
+        <v>694.35</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1607-25-CM26</t>
+          <t>1230851-55-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5469,27 +5465,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>65.061.839-4</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5499,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5514,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>189.15</v>
+        <v>255.91</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1596-78-CM26</t>
+          <t>1230851-56-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5530,12 +5526,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5545,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>65.061.839-4</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5575,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>769.34</v>
+        <v>213.82</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1607-30-CM26</t>
+          <t>4134-515-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5591,12 +5587,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5606,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5621,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5636,43 +5632,43 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>298.98</v>
+        <v>712.47</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1607-32-CM26</t>
+          <t>4134-523-SE26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-23-LP10</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5682,28 +5678,32 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>586.37</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3385-71-CM26</t>
+          <t>4885-100-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5713,12 +5713,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5728,12 +5728,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5743,12 +5743,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5758,13 +5758,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>447.32</v>
+        <v>716.61</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1607-34-CM26</t>
+          <t>4885-101-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5819,13 +5819,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>222.17</v>
+        <v>653.02</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1607-39-CM26</t>
+          <t>1596-223-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5835,27 +5835,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5880,13 +5880,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>579.26</v>
+        <v>65.44</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1607-40-CM26</t>
+          <t>1596-221-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5896,27 +5896,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>790.5599999999999</v>
+        <v>214.75</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1607-41-CM26</t>
+          <t>4134-688-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5957,12 +5957,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6002,2329 +6002,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>871.58</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2177-44-CM26</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>abr-2026</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>60.301.001-9</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>1607-45-CM26</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>abr-2026</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>61.509.000-k</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Superintendencia de Seguridad Social</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="n">
-        <v>685.59</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>1607-48-CM26</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>61.509.000-k</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Superintendencia de Seguridad Social</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="n">
-        <v>280.88</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>1978-424-CM26</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>61.606.900-4</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="n">
-        <v>157.64</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>1596-128-CM26</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>72.227.000-2</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>495.28</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>1596-127-CM26</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>72.227.000-2</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>SKY AIRLINE S A</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>88.417.000-1</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="n">
-        <v>527.67</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>1596-131-CM26</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>72.227.000-2</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>SKY AIRLINE S A</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>88.417.000-1</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="n">
-        <v>265.32</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>1596-132-CM26</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>72.227.000-2</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="n">
-        <v>249.04</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>4885-60-CM26</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>61.976.200-2</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Maule</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="n">
-        <v>406.94</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>4885-61-CM26</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>61.976.200-2</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Maule</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>683.04</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>1596-134-CM26</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>72.227.000-2</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="n">
-        <v>993.8099999999999</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>4134-334-CM26</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>69.110.200-9</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>I. Municipalidad Sagrada Familia</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="n">
-        <v>439.52</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>1607-64-CM26</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>61.509.000-k</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Superintendencia de Seguridad Social</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="n">
-        <v>164.6</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>3469-244-CM26</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>69.120.300-k</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="n">
-        <v>1599.33</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>1347775-9-CM26</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>62.000.890-7</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="n">
-        <v>363.69</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2595-226-CM26</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>69.130.700-K</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>SKY AIRLINE S A</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>88.417.000-1</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M107" s="2" t="n">
-        <v>429.08</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>1596-147-CM26</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>72.227.000-2</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M108" s="2" t="n">
-        <v>491.1</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>1596-148-CM26</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>72.227.000-2</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>SKY AIRLINE S A</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>88.417.000-1</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="n">
-        <v>514.45</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>3206-211-CM26</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>69.264.500-6</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M110" s="2" t="n">
-        <v>788.45</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>4134-394-CM26</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>69.110.200-9</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>I. Municipalidad Sagrada Familia</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>JETSMART</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>76.574.879-8</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M111" s="2" t="n">
-        <v>305.28</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>4134-395-CM26</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>69.110.200-9</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>I. Municipalidad Sagrada Familia</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>JETSMART</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>76.574.879-8</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M112" s="2" t="n">
-        <v>76.31999999999999</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2291-1051-CM26</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>69.110.400-1</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M113" s="2" t="n">
-        <v>404.14</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>1978-571-CM26</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>61.606.900-4</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>SKY AIRLINE S A</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>88.417.000-1</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M114" s="2" t="n">
-        <v>71.18000000000001</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>1607-72-CM26</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>61.509.000-k</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Superintendencia de Seguridad Social</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>277.31</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>1133353-38-CM26</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>69.100.400-7</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>3876-118-CM26</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>69.100.400-7</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M117" s="2" t="n">
-        <v>1315.07</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>3843-144-CM26</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>69.100.400-7</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M118" s="2" t="n">
-        <v>438.36</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2177-61-CM26</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>60.301.001-9</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M119" s="2" t="n">
-        <v>478.97</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>1230851-52-CM26</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>65.061.839-4</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M120" s="2" t="n">
-        <v>694.35</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>1230851-55-CM26</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>65.061.839-4</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M121" s="2" t="n">
-        <v>255.91</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>1230851-56-CM26</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>65.061.839-4</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>SKY AIRLINE S A</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>88.417.000-1</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M122" s="2" t="n">
-        <v>213.82</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>4134-515-CM26</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>69.110.200-9</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>I. Municipalidad Sagrada Familia</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>JETSMART</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>76.574.879-8</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M123" s="2" t="n">
-        <v>712.47</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>4134-523-SE26</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>2239-23-LP10</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>69.110.200-9</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>I. Municipalidad Sagrada Familia</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>JETSMART</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>76.574.879-8</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M124" s="2" t="n">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>1607-91-CM26</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>61.509.000-k</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Superintendencia de Seguridad Social</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>175.64</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>4885-100-CM26</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>61.976.200-2</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M126" s="2" t="n">
-        <v>716.61</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>4885-101-CM26</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>61.976.200-2</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>653.02</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>1596-221-CM26</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>72.227.000-2</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M128" s="2" t="n">
-        <v>214.75</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>1596-223-CM26</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>72.227.000-2</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>SKY AIRLINE S A</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>88.417.000-1</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M129" s="2" t="n">
-        <v>65.44</v>
+        <v>1258.59</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/pasajes-aereos-nacionales/maule.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/maule.xlsx
@@ -562,7 +562,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5751,7 +6087,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +6152,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6217,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5934,7 +6282,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6347,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/pasajes-aereos-nacionales/maule.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2854,7 +2854,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4885-69-CM25</t>
+          <t>4885-70-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2913,13 +2913,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>179.95</v>
+        <v>1704.37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4885-70-CM25</t>
+          <t>4885-69-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1704.37</v>
+        <v>179.95</v>
       </c>
     </row>
     <row r="40">
@@ -3634,7 +3634,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1596-375-CM25</t>
+          <t>1596-374-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3693,13 +3693,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>345.5</v>
+        <v>194.62</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1596-374-CM25</t>
+          <t>1596-375-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>194.62</v>
+        <v>345.5</v>
       </c>
     </row>
     <row r="52">
@@ -4349,7 +4349,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1596-127-CM26</t>
+          <t>1596-128-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>527.67</v>
+        <v>495.28</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1596-128-CM26</t>
+          <t>1596-127-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>495.28</v>
+        <v>527.67</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1596-131-CM26</t>
+          <t>4885-60-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4499,17 +4499,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>265.32</v>
+        <v>406.94</v>
       </c>
     </row>
     <row r="64">
@@ -4609,7 +4609,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4885-60-CM26</t>
+          <t>4885-61-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>406.94</v>
+        <v>683.04</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4885-61-CM26</t>
+          <t>1596-131-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4694,17 +4694,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.976.200-2</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>683.04</v>
+        <v>265.32</v>
       </c>
     </row>
     <row r="67">
@@ -5194,7 +5194,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4134-394-CM26</t>
+          <t>4134-395-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5253,13 +5253,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>305.28</v>
+        <v>76.31999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4134-395-CM26</t>
+          <t>4134-394-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5318,7 +5318,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>76.31999999999999</v>
+        <v>305.28</v>
       </c>
     </row>
     <row r="76">
@@ -5389,7 +5389,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1133353-38-CM26</t>
+          <t>1978-571-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5409,17 +5409,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5448,13 +5448,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1245</v>
+        <v>71.18000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1978-571-CM26</t>
+          <t>1133353-38-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5474,17 +5474,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>71.18000000000001</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="79">
@@ -6169,7 +6169,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1596-223-CM26</t>
+          <t>1596-221-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6228,13 +6228,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>65.44</v>
+        <v>214.75</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1596-221-CM26</t>
+          <t>1596-223-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>214.75</v>
+        <v>65.44</v>
       </c>
     </row>
     <row r="91">
@@ -6359,6 +6359,201 @@
       </c>
       <c r="M91" s="2" t="n">
         <v>1258.59</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1681-761-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>61.606.917-9</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>187.33</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1681-762-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>61.606.917-9</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1607-133-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>166.41</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/pasajes-aereos-nacionales/maule.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M94"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1087105-5-CM25</t>
+          <t>1068241-2-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>223.67</v>
+        <v>370.58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1068241-5-CM25</t>
+          <t>1087105-5-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -594,22 +594,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -619,12 +619,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>92.45999999999999</v>
+        <v>223.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1391-376-CM25</t>
+          <t>1068241-5-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -669,12 +669,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>126.28</v>
+        <v>92.45999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1087105-7-CM25</t>
+          <t>1391-376-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -724,22 +724,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -749,12 +749,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>320.56</v>
+        <v>126.28</v>
       </c>
     </row>
     <row r="6">
@@ -839,7 +839,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>732-169-CM25</t>
+          <t>1087105-7-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -854,22 +854,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.701.000-3</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -898,13 +898,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>55.63</v>
+        <v>320.56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>732-184-CM25</t>
+          <t>732-169-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>154.67</v>
+        <v>55.63</v>
       </c>
     </row>
     <row r="9">
@@ -1034,7 +1034,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1068241-10-CM25</t>
+          <t>732-184-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>160.48</v>
+        <v>154.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>732-197-CM25</t>
+          <t>1068241-10-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.701.000-3</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>203.6</v>
+        <v>160.48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>732-196-CM25</t>
+          <t>732-197-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1223,13 +1223,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>99.42</v>
+        <v>203.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>732-201-CM25</t>
+          <t>732-196-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1288,13 +1288,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>337.35</v>
+        <v>99.42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>732-207-CM25</t>
+          <t>732-201-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>199.42</v>
+        <v>337.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>732-215-CM25</t>
+          <t>732-207-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>283.01</v>
+        <v>199.42</v>
       </c>
     </row>
     <row r="16">
@@ -1489,7 +1489,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>732-213-CM25</t>
+          <t>732-215-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1548,13 +1548,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>290.14</v>
+        <v>283.01</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>732-224-CM25</t>
+          <t>732-213-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>615.96</v>
+        <v>290.14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2318-365-CM25</t>
+          <t>732-226-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1678,13 +1678,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2329.94</v>
+        <v>307.98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2318-366-CM25</t>
+          <t>732-224-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>514.22</v>
+        <v>615.96</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>732-226-CM25</t>
+          <t>2318-365-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.701.000-3</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1808,13 +1808,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>307.98</v>
+        <v>2329.94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>732-231-CM25</t>
+          <t>2318-366-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.701.000-3</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>841.79</v>
+        <v>514.22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>732-230-CM25</t>
+          <t>732-231-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1938,13 +1938,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>186.76</v>
+        <v>841.79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>732-240-CM25</t>
+          <t>732-230-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>216.33</v>
+        <v>186.76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2177-51-CM25</t>
+          <t>732-240-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2019,27 +2019,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>316.35</v>
+        <v>216.33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1208102-21-CM25</t>
+          <t>2177-51-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2089,22 +2089,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>309.99</v>
+        <v>316.35</v>
       </c>
     </row>
     <row r="27">
@@ -2204,7 +2204,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1208102-24-CM25</t>
+          <t>1208102-21-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>183.78</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1872-6-CM25</t>
+          <t>1208102-24-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.704.000-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE TURISMO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2328,13 +2328,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>102.57</v>
+        <v>183.78</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1596-164-CM25</t>
+          <t>1872-6-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>60.704.000-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>104.16</v>
+        <v>102.57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2177-66-CM25</t>
+          <t>1596-164-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2414,22 +2414,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2439,12 +2439,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>256.96</v>
+        <v>104.16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1230851-30-CM25</t>
+          <t>2177-66-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2474,27 +2474,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>65.061.839-4</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>227.66</v>
+        <v>256.96</v>
       </c>
     </row>
     <row r="33">
@@ -2594,7 +2594,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1230851-32-CM25</t>
+          <t>1230851-30-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>143.72</v>
+        <v>227.66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3206-228-CM25</t>
+          <t>1230851-32-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.264.500-6</t>
+          <t>65.061.839-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1397.95</v>
+        <v>143.72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1596-189-CM25</t>
+          <t>3206-228-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>252.53</v>
+        <v>1397.95</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2318-712-CM25</t>
+          <t>1596-189-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>594.88</v>
+        <v>252.53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4885-70-CM25</t>
+          <t>2318-712-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.976.200-2</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2913,13 +2913,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1704.37</v>
+        <v>594.88</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4885-69-CM25</t>
+          <t>4885-70-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2978,13 +2978,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>179.95</v>
+        <v>1704.37</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1391-1611-CM25</t>
+          <t>4885-69-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,27 +2994,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3043,13 +3043,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>253.91</v>
+        <v>179.95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1596-231-CM25</t>
+          <t>1391-1611-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3108,13 +3108,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>779.88</v>
+        <v>253.91</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1391-1688-CM25</t>
+          <t>1596-231-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>497.98</v>
+        <v>779.88</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2177-82-CM25</t>
+          <t>1391-1688-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3194,22 +3194,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3238,13 +3238,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>316.89</v>
+        <v>497.98</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1208102-54-CM25</t>
+          <t>2177-82-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3254,27 +3254,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>160.36</v>
+        <v>316.89</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4885-139-CM25</t>
+          <t>1208102-54-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.976.200-2</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>711.89</v>
+        <v>160.36</v>
       </c>
     </row>
     <row r="46">
@@ -3439,7 +3439,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1872-14-CM25</t>
+          <t>4885-139-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.704.000-1</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE TURISMO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3498,13 +3498,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>437.36</v>
+        <v>711.89</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4885-192-CM25</t>
+          <t>1872-14-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.976.200-2</t>
+          <t>60.704.000-1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3563,13 +3563,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1792.81</v>
+        <v>437.36</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4885-195-CM25</t>
+          <t>4885-192-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3628,13 +3628,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>452.96</v>
+        <v>1792.81</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1596-374-CM25</t>
+          <t>4885-195-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>194.62</v>
+        <v>452.96</v>
       </c>
     </row>
     <row r="51">
@@ -3764,7 +3764,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4134-28-CM26</t>
+          <t>1596-374-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3774,12 +3774,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3823,13 +3823,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1286.54</v>
+        <v>194.62</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1234683-13-CM26</t>
+          <t>4134-28-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3839,27 +3839,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>65.145.951-6</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL  DE DEPORTES  DE SAN CLEMENTE</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3888,13 +3888,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>152.31</v>
+        <v>1286.54</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1978-157-CM26</t>
+          <t>1234683-13-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3904,27 +3904,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>65.145.951-6</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>CORPORACION MUNICIPAL  DE DEPORTES  DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3934,12 +3934,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>270.59</v>
+        <v>152.31</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1978-158-CM26</t>
+          <t>1978-157-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>128.67</v>
+        <v>270.59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2177-18-CM26</t>
+          <t>1978-158-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4039,22 +4039,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>285.13</v>
+        <v>128.67</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1596-78-CM26</t>
+          <t>2177-18-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4129,12 +4129,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>769.34</v>
+        <v>285.13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3385-71-CM26</t>
+          <t>1596-78-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4164,27 +4164,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4213,13 +4213,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>447.32</v>
+        <v>769.34</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2177-44-CM26</t>
+          <t>3385-71-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4234,22 +4234,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4278,13 +4278,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>93</v>
+        <v>447.32</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1978-424-CM26</t>
+          <t>2177-44-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4294,27 +4294,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4343,13 +4343,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>157.64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1596-128-CM26</t>
+          <t>1978-424-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4364,22 +4364,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>495.28</v>
+        <v>157.64</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1596-127-CM26</t>
+          <t>1596-128-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>527.67</v>
+        <v>495.28</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4885-60-CM26</t>
+          <t>1596-127-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4494,22 +4494,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.976.200-2</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>406.94</v>
+        <v>527.67</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1596-132-CM26</t>
+          <t>4885-61-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>249.04</v>
+        <v>683.04</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4885-61-CM26</t>
+          <t>1596-131-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4629,17 +4629,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.976.200-2</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>683.04</v>
+        <v>265.32</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1596-131-CM26</t>
+          <t>4885-60-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4694,17 +4694,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4733,13 +4733,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>265.32</v>
+        <v>406.94</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1596-134-CM26</t>
+          <t>1596-132-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4798,13 +4798,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>993.8099999999999</v>
+        <v>249.04</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4134-334-CM26</t>
+          <t>1596-134-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4819,22 +4819,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>439.52</v>
+        <v>993.8099999999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3469-244-CM26</t>
+          <t>4134-334-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4928,13 +4928,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1599.33</v>
+        <v>439.52</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2595-226-CM26</t>
+          <t>3469-244-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>69.120.300-k</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4993,13 +4993,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>429.08</v>
+        <v>1599.33</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1596-147-CM26</t>
+          <t>2595-226-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5058,13 +5058,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>491.1</v>
+        <v>429.08</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1596-148-CM26</t>
+          <t>1596-147-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5123,13 +5123,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>514.45</v>
+        <v>491.1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3206-211-CM26</t>
+          <t>1596-148-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5144,22 +5144,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.264.500-6</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>788.45</v>
+        <v>514.45</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4134-395-CM26</t>
+          <t>3206-211-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5253,13 +5253,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>76.31999999999999</v>
+        <v>788.45</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4134-394-CM26</t>
+          <t>4134-395-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5318,13 +5318,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>305.28</v>
+        <v>76.31999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2291-1051-CM26</t>
+          <t>4134-394-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5383,13 +5383,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>404.14</v>
+        <v>305.28</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1978-571-CM26</t>
+          <t>2291-1051-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5404,22 +5404,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>71.18000000000001</v>
+        <v>404.14</v>
       </c>
     </row>
     <row r="78">
@@ -5519,7 +5519,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3843-144-CM26</t>
+          <t>1978-571-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>438.36</v>
+        <v>71.18000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3876-118-CM26</t>
+          <t>3843-144-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5643,13 +5643,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1315.07</v>
+        <v>438.36</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2177-61-CM26</t>
+          <t>3876-118-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>478.97</v>
+        <v>1315.07</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1230851-52-CM26</t>
+          <t>2177-61-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>65.061.839-4</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5773,13 +5773,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>694.35</v>
+        <v>478.97</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1230851-55-CM26</t>
+          <t>1230851-52-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5838,13 +5838,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>255.91</v>
+        <v>694.35</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1230851-56-CM26</t>
+          <t>1230851-55-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5903,13 +5903,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>213.82</v>
+        <v>255.91</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4134-515-CM26</t>
+          <t>1230851-56-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>65.061.839-4</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5949,12 +5949,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5968,18 +5968,18 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>712.47</v>
+        <v>213.82</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4134-523-SE26</t>
+          <t>4134-515-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5989,12 +5989,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6033,43 +6033,43 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>7.4</v>
+        <v>712.47</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4885-100-CM26</t>
+          <t>4134-523-SE26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-23-LP10</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.976.200-2</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6098,13 +6098,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>716.61</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4885-101-CM26</t>
+          <t>4885-100-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6163,13 +6163,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>653.02</v>
+        <v>716.61</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1596-221-CM26</t>
+          <t>4885-101-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6184,22 +6184,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.976.200-2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>214.75</v>
+        <v>653.02</v>
       </c>
     </row>
     <row r="90">
@@ -6299,7 +6299,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4134-688-CM26</t>
+          <t>1596-221-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6309,27 +6309,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6358,13 +6358,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1258.59</v>
+        <v>214.75</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1681-761-CM26</t>
+          <t>4134-688-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6423,13 +6423,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>187.33</v>
+        <v>1258.59</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1681-762-CM26</t>
+          <t>1681-761-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6488,71 +6488,136 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>75</v>
+        <v>187.33</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>1681-762-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>61.606.917-9</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>1607-133-CM26</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>61.509.000-k</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
         <is>
           <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="n">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
         <v>166.41</v>
       </c>
     </row>
